--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8728,0.0185,0.0210,0.0444</t>
-  </si>
-  <si>
-    <t>0.0128,0.0147,0.0060,0.9890</t>
-  </si>
-  <si>
-    <t>0.7266,0.0282,0.0445,0.2095</t>
-  </si>
-  <si>
-    <t>0.0131,0.0010,0.0035,0.9928</t>
-  </si>
-  <si>
-    <t>0.9924,0.0011,0.0004,0.0024</t>
-  </si>
-  <si>
-    <t>0.9911,0.0018,0.0002,0.0023</t>
-  </si>
-  <si>
-    <t>0.9848,0.0028,0.0014,0.0050</t>
-  </si>
-  <si>
-    <t>0.9961,0.0015,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9782,0.0106,0.0008,0.0051</t>
-  </si>
-  <si>
-    <t>0.9915,0.0067,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9975,0.0005,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9961,0.0002,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.8437,0.0235,0.1208,0.0057</t>
-  </si>
-  <si>
-    <t>0.2706,0.0161,0.7880,0.0076</t>
-  </si>
-  <si>
-    <t>0.5098,0.0105,0.6934,0.0014</t>
-  </si>
-  <si>
-    <t>0.1190,0.0481,0.8605,0.0086</t>
-  </si>
-  <si>
-    <t>0.8767,0.0568,0.0368,0.0041</t>
-  </si>
-  <si>
-    <t>0.0060,0.9896,0.0026,0.0003</t>
-  </si>
-  <si>
-    <t>0.0425,0.9651,0.0069,0.0007</t>
-  </si>
-  <si>
-    <t>0.2820,0.8043,0.0137,0.0026</t>
-  </si>
-  <si>
-    <t>0.0757,0.9476,0.0031,0.0010</t>
-  </si>
-  <si>
-    <t>0.0073,0.9892,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.6550,0.0244,0.2743,0.0553</t>
-  </si>
-  <si>
-    <t>0.5246,0.0068,0.3694,0.0396</t>
-  </si>
-  <si>
-    <t>0.1092,0.0161,0.8733,0.0067</t>
-  </si>
-  <si>
-    <t>0.0120,0.0103,0.9669,0.0089</t>
-  </si>
-  <si>
-    <t>0.0164,0.0061,0.9554,0.0321</t>
-  </si>
-  <si>
-    <t>0.0345,0.0031,0.9041,0.0971</t>
-  </si>
-  <si>
-    <t>0.0067,0.0031,0.9927,0.0004</t>
-  </si>
-  <si>
-    <t>0.2588,0.7806,0.0099,0.0041</t>
-  </si>
-  <si>
-    <t>0.1837,0.5758,0.4180,0.0088</t>
-  </si>
-  <si>
-    <t>0.0028,0.0066,0.9869,0.0084</t>
-  </si>
-  <si>
-    <t>0.0107,0.9144,0.1428,0.0001</t>
-  </si>
-  <si>
-    <t>0.8990,0.0898,0.0112,0.0069</t>
-  </si>
-  <si>
-    <t>0.4121,0.3206,0.2908,0.0095</t>
-  </si>
-  <si>
-    <t>0.7091,0.3884,0.0115,0.0028</t>
-  </si>
-  <si>
-    <t>0.1318,0.8594,0.0150,0.0148</t>
-  </si>
-  <si>
-    <t>0.0052,0.2858,0.8694,0.0065</t>
-  </si>
-  <si>
-    <t>0.1081,0.0085,0.8776,0.0253</t>
-  </si>
-  <si>
-    <t>0.0296,0.2103,0.9126,0.0148</t>
-  </si>
-  <si>
-    <t>0.0836,0.0123,0.8528,0.0748</t>
-  </si>
-  <si>
-    <t>0.0149,0.3761,0.9252,0.0030</t>
-  </si>
-  <si>
-    <t>0.0023,0.9844,0.0078,0.0000</t>
-  </si>
-  <si>
-    <t>0.0051,0.0085,0.9784,0.0115</t>
-  </si>
-  <si>
-    <t>0.0377,0.8196,0.0377,0.4453</t>
-  </si>
-  <si>
-    <t>0.0054,0.9838,0.0043,0.0020</t>
-  </si>
-  <si>
-    <t>0.0042,0.9525,0.3190,0.0018</t>
-  </si>
-  <si>
-    <t>0.0017,0.9925,0.0130,0.0003</t>
-  </si>
-  <si>
-    <t>0.0011,0.0086,0.9873,0.0081</t>
-  </si>
-  <si>
-    <t>0.0265,0.0182,0.9719,0.0020</t>
-  </si>
-  <si>
-    <t>0.0400,0.0160,0.9562,0.0024</t>
-  </si>
-  <si>
-    <t>0.0624,0.0036,0.9558,0.0013</t>
-  </si>
-  <si>
-    <t>0.0097,0.0149,0.9752,0.0048</t>
-  </si>
-  <si>
-    <t>0.0101,0.0548,0.9481,0.0145</t>
-  </si>
-  <si>
-    <t>0.9674,0.0281,0.0024,0.0028</t>
-  </si>
-  <si>
-    <t>0.9540,0.0206,0.0203,0.0047</t>
-  </si>
-  <si>
-    <t>0.9525,0.0474,0.0047,0.0019</t>
-  </si>
-  <si>
-    <t>0.0010,0.0054,0.9912,0.0123</t>
-  </si>
-  <si>
-    <t>0.9623,0.0242,0.0033,0.0065</t>
-  </si>
-  <si>
-    <t>0.9870,0.0109,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9827,0.0116,0.0017,0.0012</t>
-  </si>
-  <si>
-    <t>0.0015,0.7592,0.9640,0.0009</t>
-  </si>
-  <si>
-    <t>0.0115,0.0110,0.9543,0.0284</t>
-  </si>
-  <si>
-    <t>0.0107,0.0673,0.9559,0.0141</t>
-  </si>
-  <si>
-    <t>0.0002,0.9245,0.9811,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0055,0.9885,0.0101</t>
-  </si>
-  <si>
-    <t>0.1109,0.8682,0.0310,0.0045</t>
-  </si>
-  <si>
-    <t>0.0080,0.9839,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.8587,0.0696,0.0449,0.0127</t>
-  </si>
-  <si>
-    <t>0.3727,0.6333,0.1060,0.0071</t>
-  </si>
-  <si>
-    <t>0.0033,0.0223,0.9763,0.0071</t>
-  </si>
-  <si>
-    <t>0.0006,0.8934,0.9325,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9737,0.8522,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9869,0.4864,0.0004</t>
-  </si>
-  <si>
-    <t>0.0008,0.9237,0.7935,0.0002</t>
-  </si>
-  <si>
-    <t>0.0378,0.0007,0.0107,0.9684</t>
-  </si>
-  <si>
-    <t>0.0016,0.0029,0.0004,0.9988</t>
-  </si>
-  <si>
-    <t>0.0075,0.0051,0.0004,0.9961</t>
-  </si>
-  <si>
-    <t>0.0267,0.0096,0.0015,0.9869</t>
-  </si>
-  <si>
-    <t>0.0304,0.0008,0.0011,0.9908</t>
-  </si>
-  <si>
-    <t>0.0019,0.0138,0.0006,0.9977</t>
-  </si>
-  <si>
-    <t>0.0005,0.9691,0.8632,0.0001</t>
-  </si>
-  <si>
-    <t>0.0035,0.3466,0.9767,0.0009</t>
-  </si>
-  <si>
-    <t>0.0056,0.8014,0.8353,0.0023</t>
-  </si>
-  <si>
-    <t>0.0137,0.4450,0.9123,0.0028</t>
-  </si>
-  <si>
-    <t>0.0004,0.9743,0.7661,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9312,0.6719,0.0001</t>
-  </si>
-  <si>
-    <t>0.9622,0.0412,0.0057,0.0010</t>
-  </si>
-  <si>
-    <t>0.9701,0.0317,0.0047,0.0009</t>
-  </si>
-  <si>
-    <t>0.9696,0.0308,0.0041,0.0015</t>
-  </si>
-  <si>
-    <t>0.9684,0.0269,0.0008,0.0027</t>
-  </si>
-  <si>
-    <t>0.9862,0.0106,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.9904,0.0045,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.9615,0.0378,0.0041,0.0016</t>
-  </si>
-  <si>
-    <t>0.9744,0.0285,0.0015,0.0011</t>
-  </si>
-  <si>
-    <t>0.9895,0.0013,0.0001,0.0045</t>
-  </si>
-  <si>
-    <t>0.9955,0.0005,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9968,0.0003,0.0000,0.0011</t>
-  </si>
-  <si>
-    <t>0.9970,0.0005,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9937,0.0010,0.0000,0.0020</t>
-  </si>
-  <si>
-    <t>0.9925,0.0037,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.9922,0.0019,0.0006,0.0016</t>
-  </si>
-  <si>
-    <t>0.9924,0.0022,0.0013,0.0009</t>
-  </si>
-  <si>
-    <t>0.0014,0.0016,0.9898,0.0192</t>
-  </si>
-  <si>
-    <t>0.0629,0.0547,0.8756,0.0226</t>
-  </si>
-  <si>
-    <t>0.7358,0.0080,0.1287,0.0672</t>
-  </si>
-  <si>
-    <t>0.0928,0.0167,0.9204,0.0007</t>
-  </si>
-  <si>
-    <t>0.0236,0.9644,0.0027,0.0021</t>
-  </si>
-  <si>
-    <t>0.0068,0.9850,0.0028,0.0008</t>
-  </si>
-  <si>
-    <t>0.1053,0.8930,0.0014,0.0019</t>
-  </si>
-  <si>
-    <t>0.0798,0.9071,0.0036,0.0074</t>
-  </si>
-  <si>
-    <t>0.0269,0.9663,0.0177,0.0012</t>
-  </si>
-  <si>
-    <t>0.0104,0.9807,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.6257,0.4714,0.0147,0.0037</t>
-  </si>
-  <si>
-    <t>0.8475,0.0250,0.1154,0.0076</t>
-  </si>
-  <si>
-    <t>0.1176,0.0170,0.9095,0.0031</t>
-  </si>
-  <si>
-    <t>0.4018,0.1434,0.4582,0.0067</t>
-  </si>
-  <si>
-    <t>0.4086,0.1235,0.4046,0.0046</t>
-  </si>
-  <si>
-    <t>0.3277,0.2421,0.3079,0.3977</t>
-  </si>
-  <si>
-    <t>0.0022,0.9914,0.0101,0.0004</t>
-  </si>
-  <si>
-    <t>0.0041,0.9738,0.0406,0.0055</t>
-  </si>
-  <si>
-    <t>0.1002,0.7795,0.0169,0.2255</t>
-  </si>
-  <si>
-    <t>0.0005,0.9477,0.9165,0.0001</t>
-  </si>
-  <si>
-    <t>0.0123,0.9728,0.1021,0.0010</t>
-  </si>
-  <si>
-    <t>0.4827,0.5730,0.0324,0.0008</t>
-  </si>
-  <si>
-    <t>0.4324,0.7132,0.0075,0.0019</t>
-  </si>
-  <si>
-    <t>0.9831,0.0085,0.0011,0.0021</t>
-  </si>
-  <si>
-    <t>0.9917,0.0008,0.0008,0.0025</t>
-  </si>
-  <si>
-    <t>0.9827,0.0005,0.0003,0.0153</t>
-  </si>
-  <si>
-    <t>0.9855,0.0029,0.0032,0.0024</t>
-  </si>
-  <si>
-    <t>0.9835,0.0005,0.0001,0.0168</t>
-  </si>
-  <si>
-    <t>0.9682,0.0286,0.0039,0.0013</t>
-  </si>
-  <si>
-    <t>0.9718,0.0021,0.0018,0.0182</t>
-  </si>
-  <si>
-    <t>0.9905,0.0010,0.0021,0.0017</t>
-  </si>
-  <si>
-    <t>0.0008,0.8001,0.9685,0.0002</t>
-  </si>
-  <si>
-    <t>0.0052,0.4493,0.9621,0.0002</t>
-  </si>
-  <si>
-    <t>0.0039,0.1909,0.9693,0.0008</t>
-  </si>
-  <si>
-    <t>0.0273,0.0628,0.9633,0.0002</t>
-  </si>
-  <si>
-    <t>0.7864,0.0379,0.0933,0.0406</t>
-  </si>
-  <si>
-    <t>0.8306,0.0358,0.1079,0.0072</t>
-  </si>
-  <si>
-    <t>0.6852,0.0109,0.3810,0.0138</t>
-  </si>
-  <si>
-    <t>0.6628,0.1132,0.2238,0.0183</t>
-  </si>
-  <si>
-    <t>0.1635,0.0044,0.0050,0.9173</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.0006,0.9995</t>
-  </si>
-  <si>
-    <t>0.0051,0.0805,0.0026,0.9890</t>
-  </si>
-  <si>
-    <t>0.0181,0.0011,0.0024,0.9917</t>
-  </si>
-  <si>
-    <t>0.0049,0.9182,0.3125,0.0028</t>
-  </si>
-  <si>
-    <t>0.9609,0.0278,0.0072,0.0024</t>
-  </si>
-  <si>
-    <t>0.3416,0.7046,0.0124,0.0065</t>
-  </si>
-  <si>
-    <t>0.9825,0.0095,0.0014,0.0013</t>
-  </si>
-  <si>
-    <t>0.8343,0.2018,0.0168,0.0012</t>
-  </si>
-  <si>
-    <t>0.9553,0.0104,0.0108,0.0072</t>
-  </si>
-  <si>
-    <t>0.5900,0.0209,0.0219,0.4143</t>
-  </si>
-  <si>
-    <t>0.9607,0.0174,0.0201,0.0023</t>
-  </si>
-  <si>
-    <t>0.0020,0.0072,0.9848,0.0237</t>
-  </si>
-  <si>
-    <t>0.9701,0.0014,0.0052,0.0082</t>
-  </si>
-  <si>
-    <t>0.9628,0.0014,0.0027,0.0232</t>
-  </si>
-  <si>
-    <t>0.0609,0.9249,0.0109,0.0071</t>
-  </si>
-  <si>
-    <t>0.8422,0.1307,0.0137,0.0076</t>
-  </si>
-  <si>
-    <t>0.8667,0.0777,0.0476,0.0065</t>
-  </si>
-  <si>
-    <t>0.5516,0.4430,0.0426,0.0281</t>
-  </si>
-  <si>
-    <t>0.8721,0.1279,0.0173,0.0028</t>
-  </si>
-  <si>
-    <t>0.8617,0.1099,0.0272,0.0047</t>
-  </si>
-  <si>
-    <t>0.9865,0.0040,0.0011,0.0028</t>
-  </si>
-  <si>
-    <t>0.9906,0.0028,0.0005,0.0017</t>
-  </si>
-  <si>
-    <t>0.9899,0.0027,0.0005,0.0021</t>
-  </si>
-  <si>
-    <t>0.9907,0.0003,0.0002,0.0063</t>
-  </si>
-  <si>
-    <t>0.9817,0.0098,0.0021,0.0021</t>
-  </si>
-  <si>
-    <t>0.9840,0.0085,0.0033,0.0011</t>
-  </si>
-  <si>
-    <t>0.9801,0.0025,0.0006,0.0108</t>
-  </si>
-  <si>
-    <t>0.9966,0.0008,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.2730,0.7474,0.0120,0.0120</t>
-  </si>
-  <si>
-    <t>0.8340,0.2257,0.0194,0.0018</t>
-  </si>
-  <si>
-    <t>0.7814,0.3129,0.0061,0.0027</t>
-  </si>
-  <si>
-    <t>0.6736,0.3184,0.0782,0.0183</t>
-  </si>
-  <si>
-    <t>0.9061,0.1579,0.0027,0.0008</t>
-  </si>
-  <si>
-    <t>0.9331,0.0328,0.0141,0.0099</t>
-  </si>
-  <si>
-    <t>0.9212,0.0911,0.0043,0.0031</t>
-  </si>
-  <si>
-    <t>0.8338,0.2347,0.0067,0.0029</t>
-  </si>
-  <si>
-    <t>0.0006,0.0073,0.9970,0.0008</t>
-  </si>
-  <si>
-    <t>0.9207,0.0528,0.0186,0.0071</t>
-  </si>
-  <si>
-    <t>0.0050,0.1314,0.9555,0.0010</t>
-  </si>
-  <si>
-    <t>0.0028,0.1703,0.9782,0.0017</t>
-  </si>
-  <si>
-    <t>0.1107,0.0231,0.8984,0.0061</t>
-  </si>
-  <si>
-    <t>0.0087,0.3086,0.9582,0.0004</t>
-  </si>
-  <si>
-    <t>0.0033,0.0452,0.9861,0.0007</t>
-  </si>
-  <si>
-    <t>0.0016,0.0032,0.9954,0.0007</t>
-  </si>
-  <si>
-    <t>0.0040,0.0111,0.9877,0.0011</t>
-  </si>
-  <si>
-    <t>0.3549,0.0685,0.6290,0.0746</t>
-  </si>
-  <si>
-    <t>0.3084,0.0452,0.6995,0.0055</t>
-  </si>
-  <si>
-    <t>0.1945,0.0952,0.7838,0.0120</t>
-  </si>
-  <si>
-    <t>0.2713,0.3320,0.3744,0.0068</t>
-  </si>
-  <si>
-    <t>0.2446,0.5211,0.2877,0.0178</t>
-  </si>
-  <si>
-    <t>0.4197,0.1027,0.5330,0.0287</t>
-  </si>
-  <si>
-    <t>0.6949,0.0960,0.0474,0.1310</t>
-  </si>
-  <si>
-    <t>0.6335,0.0214,0.5236,0.0028</t>
-  </si>
-  <si>
-    <t>0.1997,0.8140,0.0244,0.0009</t>
-  </si>
-  <si>
-    <t>0.2835,0.8014,0.0059,0.0009</t>
-  </si>
-  <si>
-    <t>0.9333,0.0872,0.0026,0.0021</t>
-  </si>
-  <si>
-    <t>0.8880,0.1721,0.0051,0.0018</t>
-  </si>
-  <si>
-    <t>0.7228,0.4005,0.0072,0.0018</t>
-  </si>
-  <si>
-    <t>0.3698,0.1765,0.5194,0.0062</t>
-  </si>
-  <si>
-    <t>0.7949,0.0230,0.1908,0.0051</t>
-  </si>
-  <si>
-    <t>0.8249,0.0090,0.0655,0.0333</t>
-  </si>
-  <si>
-    <t>0.6111,0.0195,0.3770,0.0323</t>
-  </si>
-  <si>
-    <t>0.7903,0.0957,0.0655,0.0120</t>
-  </si>
-  <si>
-    <t>0.0194,0.0122,0.9432,0.0390</t>
-  </si>
-  <si>
-    <t>0.0113,0.6507,0.8288,0.0044</t>
-  </si>
-  <si>
-    <t>0.0682,0.0674,0.8850,0.0102</t>
-  </si>
-  <si>
-    <t>0.1017,0.0151,0.8555,0.0580</t>
-  </si>
-  <si>
-    <t>0.0130,0.7871,0.5001,0.0034</t>
-  </si>
-  <si>
-    <t>0.9858,0.0122,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.9431,0.0397,0.0162,0.0065</t>
-  </si>
-  <si>
-    <t>0.9480,0.0056,0.0007,0.0372</t>
-  </si>
-  <si>
-    <t>0.9918,0.0051,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9626,0.0180,0.0038,0.0082</t>
-  </si>
-  <si>
-    <t>0.9875,0.0063,0.0008,0.0018</t>
-  </si>
-  <si>
-    <t>0.9812,0.0074,0.0033,0.0031</t>
-  </si>
-  <si>
-    <t>0.9937,0.0018,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.1071,0.0187,0.8973,0.0026</t>
-  </si>
-  <si>
-    <t>0.3782,0.1664,0.5799,0.0144</t>
-  </si>
-  <si>
-    <t>0.2505,0.0141,0.3431,0.3807</t>
-  </si>
-  <si>
-    <t>0.0028,0.0116,0.9901,0.0025</t>
-  </si>
-  <si>
-    <t>0.0018,0.0074,0.9955,0.0002</t>
-  </si>
-  <si>
-    <t>0.0070,0.1074,0.9601,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0044,0.9958,0.0013</t>
-  </si>
-  <si>
-    <t>0.0891,0.0248,0.9156,0.0010</t>
-  </si>
-  <si>
-    <t>0.0022,0.0789,0.9875,0.0005</t>
-  </si>
-  <si>
-    <t>0.0125,0.1487,0.9325,0.0053</t>
-  </si>
-  <si>
-    <t>0.0748,0.1017,0.8644,0.0045</t>
-  </si>
-  <si>
-    <t>0.8325,0.0027,0.1975,0.0053</t>
-  </si>
-  <si>
-    <t>0.6863,0.0043,0.3696,0.0099</t>
-  </si>
-  <si>
-    <t>0.8087,0.0155,0.1427,0.0166</t>
-  </si>
-  <si>
-    <t>0.9896,0.0031,0.0004,0.0021</t>
-  </si>
-  <si>
-    <t>0.9817,0.0144,0.0032,0.0010</t>
-  </si>
-  <si>
-    <t>0.9968,0.0008,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9780,0.0146,0.0020,0.0026</t>
-  </si>
-  <si>
-    <t>0.9911,0.0014,0.0004,0.0024</t>
-  </si>
-  <si>
-    <t>0.9895,0.0072,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9846,0.0071,0.0004,0.0028</t>
-  </si>
-  <si>
-    <t>0.9747,0.0044,0.0004,0.0110</t>
-  </si>
-  <si>
-    <t>0.0061,0.1372,0.9358,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.0408,0.9885,0.0009</t>
-  </si>
-  <si>
-    <t>0.0031,0.0181,0.9845,0.0027</t>
-  </si>
-  <si>
-    <t>0.1525,0.0346,0.8530,0.0009</t>
-  </si>
-  <si>
-    <t>0.0034,0.0123,0.9887,0.0015</t>
-  </si>
-  <si>
-    <t>0.0583,0.0073,0.7673,0.3241</t>
-  </si>
-  <si>
-    <t>0.1316,0.0232,0.8676,0.0029</t>
-  </si>
-  <si>
-    <t>0.1814,0.0502,0.6169,0.1832</t>
-  </si>
-  <si>
-    <t>0.8819,0.0009,0.0106,0.0870</t>
-  </si>
-  <si>
-    <t>0.0388,0.0679,0.0026,0.9751</t>
-  </si>
-  <si>
-    <t>0.0310,0.0467,0.0028,0.9789</t>
-  </si>
-  <si>
-    <t>0.0036,0.0003,0.0145,0.9925</t>
-  </si>
-  <si>
-    <t>0.0046,0.0035,0.0005,0.9974</t>
-  </si>
-  <si>
-    <t>0.7340,0.0149,0.0180,0.2258</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.2330,0.4454,0.0618,0.4994</t>
+  </si>
+  <si>
+    <t>0.0196,0.0026,0.0023,0.9907</t>
+  </si>
+  <si>
+    <t>0.5428,0.0068,0.0072,0.5604</t>
+  </si>
+  <si>
+    <t>0.0905,0.0080,0.0076,0.9557</t>
+  </si>
+  <si>
+    <t>0.9961,0.0022,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9957,0.0009,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9870,0.0035,0.0006,0.0041</t>
+  </si>
+  <si>
+    <t>0.9958,0.0007,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9892,0.0035,0.0006,0.0026</t>
+  </si>
+  <si>
+    <t>0.9820,0.0129,0.0023,0.0015</t>
+  </si>
+  <si>
+    <t>0.9930,0.0009,0.0005,0.0022</t>
+  </si>
+  <si>
+    <t>0.9929,0.0006,0.0002,0.0035</t>
+  </si>
+  <si>
+    <t>0.3505,0.2209,0.4999,0.0199</t>
+  </si>
+  <si>
+    <t>0.2223,0.0302,0.8489,0.0026</t>
+  </si>
+  <si>
+    <t>0.2702,0.0193,0.8450,0.0011</t>
+  </si>
+  <si>
+    <t>0.0674,0.1739,0.7852,0.0032</t>
+  </si>
+  <si>
+    <t>0.7795,0.0662,0.1471,0.0213</t>
+  </si>
+  <si>
+    <t>0.0187,0.9765,0.0143,0.0006</t>
+  </si>
+  <si>
+    <t>0.0155,0.9817,0.0053,0.0011</t>
+  </si>
+  <si>
+    <t>0.5850,0.4827,0.0388,0.0099</t>
+  </si>
+  <si>
+    <t>0.0066,0.9887,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.0039,0.9927,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.5038,0.0234,0.5691,0.0072</t>
+  </si>
+  <si>
+    <t>0.4769,0.0328,0.5321,0.0137</t>
+  </si>
+  <si>
+    <t>0.0843,0.0044,0.9425,0.0013</t>
+  </si>
+  <si>
+    <t>0.1750,0.0521,0.8147,0.0026</t>
+  </si>
+  <si>
+    <t>0.0582,0.0036,0.9444,0.0021</t>
+  </si>
+  <si>
+    <t>0.1138,0.0032,0.9097,0.0055</t>
+  </si>
+  <si>
+    <t>0.0013,0.0142,0.9839,0.0096</t>
+  </si>
+  <si>
+    <t>0.7912,0.2794,0.0143,0.0021</t>
+  </si>
+  <si>
+    <t>0.7255,0.2886,0.0480,0.0076</t>
+  </si>
+  <si>
+    <t>0.0002,0.0078,0.9976,0.0010</t>
+  </si>
+  <si>
+    <t>0.0089,0.9382,0.0848,0.0005</t>
+  </si>
+  <si>
+    <t>0.9049,0.0472,0.0230,0.0105</t>
+  </si>
+  <si>
+    <t>0.5252,0.0729,0.3923,0.0478</t>
+  </si>
+  <si>
+    <t>0.8613,0.2104,0.0084,0.0011</t>
+  </si>
+  <si>
+    <t>0.0567,0.8424,0.4882,0.0100</t>
+  </si>
+  <si>
+    <t>0.0520,0.4217,0.6302,0.0049</t>
+  </si>
+  <si>
+    <t>0.0868,0.0270,0.8363,0.0945</t>
+  </si>
+  <si>
+    <t>0.0086,0.0101,0.9776,0.0071</t>
+  </si>
+  <si>
+    <t>0.0487,0.0058,0.9246,0.0288</t>
+  </si>
+  <si>
+    <t>0.0784,0.1773,0.8325,0.0131</t>
+  </si>
+  <si>
+    <t>0.0030,0.9446,0.0791,0.0017</t>
+  </si>
+  <si>
+    <t>0.0235,0.0327,0.9441,0.0098</t>
+  </si>
+  <si>
+    <t>0.0176,0.6696,0.0148,0.8220</t>
+  </si>
+  <si>
+    <t>0.0265,0.9336,0.0464,0.0219</t>
+  </si>
+  <si>
+    <t>0.0112,0.9526,0.1073,0.0039</t>
+  </si>
+  <si>
+    <t>0.0088,0.9658,0.0112,0.0168</t>
+  </si>
+  <si>
+    <t>0.0016,0.1769,0.9828,0.0015</t>
+  </si>
+  <si>
+    <t>0.0008,0.1563,0.9858,0.0004</t>
+  </si>
+  <si>
+    <t>0.0273,0.0212,0.9395,0.0114</t>
+  </si>
+  <si>
+    <t>0.0769,0.0030,0.9617,0.0004</t>
+  </si>
+  <si>
+    <t>0.0043,0.0814,0.9681,0.0057</t>
+  </si>
+  <si>
+    <t>0.0058,0.0225,0.9727,0.0105</t>
+  </si>
+  <si>
+    <t>0.9096,0.0911,0.0019,0.0070</t>
+  </si>
+  <si>
+    <t>0.9861,0.0052,0.0014,0.0022</t>
+  </si>
+  <si>
+    <t>0.9755,0.0135,0.0013,0.0033</t>
+  </si>
+  <si>
+    <t>0.0036,0.0074,0.9903,0.0045</t>
+  </si>
+  <si>
+    <t>0.9829,0.0106,0.0017,0.0013</t>
+  </si>
+  <si>
+    <t>0.9696,0.0243,0.0013,0.0032</t>
+  </si>
+  <si>
+    <t>0.9487,0.0642,0.0044,0.0016</t>
+  </si>
+  <si>
+    <t>0.0008,0.9627,0.8588,0.0002</t>
+  </si>
+  <si>
+    <t>0.0073,0.0284,0.9770,0.0033</t>
+  </si>
+  <si>
+    <t>0.0033,0.0077,0.9887,0.0034</t>
+  </si>
+  <si>
+    <t>0.0007,0.9733,0.6274,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9974,0.0021</t>
+  </si>
+  <si>
+    <t>0.0346,0.9208,0.0742,0.0017</t>
+  </si>
+  <si>
+    <t>0.0053,0.9883,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.5543,0.0688,0.4795,0.0090</t>
+  </si>
+  <si>
+    <t>0.1046,0.6090,0.5939,0.0306</t>
+  </si>
+  <si>
+    <t>0.0368,0.4120,0.5317,0.0013</t>
+  </si>
+  <si>
+    <t>0.0007,0.9555,0.7925,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9703,0.8452,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9964,0.0734,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9374,0.6747,0.0000</t>
+  </si>
+  <si>
+    <t>0.0122,0.0004,0.0245,0.9783</t>
+  </si>
+  <si>
+    <t>0.0013,0.0027,0.0001,0.9990</t>
+  </si>
+  <si>
+    <t>0.0169,0.0093,0.0007,0.9923</t>
+  </si>
+  <si>
+    <t>0.0170,0.0052,0.0016,0.9909</t>
+  </si>
+  <si>
+    <t>0.0343,0.0046,0.0283,0.9647</t>
+  </si>
+  <si>
+    <t>0.0032,0.0007,0.0208,0.9929</t>
+  </si>
+  <si>
+    <t>0.0004,0.9651,0.8784,0.0001</t>
+  </si>
+  <si>
+    <t>0.0038,0.8101,0.9342,0.0008</t>
+  </si>
+  <si>
+    <t>0.0011,0.6350,0.9695,0.0002</t>
+  </si>
+  <si>
+    <t>0.0262,0.4058,0.8360,0.0018</t>
+  </si>
+  <si>
+    <t>0.0001,0.9948,0.7065,0.0000</t>
+  </si>
+  <si>
+    <t>0.0102,0.7376,0.8231,0.0016</t>
+  </si>
+  <si>
+    <t>0.9888,0.0042,0.0020,0.0012</t>
+  </si>
+  <si>
+    <t>0.9263,0.1088,0.0053,0.0010</t>
+  </si>
+  <si>
+    <t>0.9545,0.0581,0.0057,0.0010</t>
+  </si>
+  <si>
+    <t>0.9914,0.0037,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9806,0.0147,0.0017,0.0016</t>
+  </si>
+  <si>
+    <t>0.9944,0.0023,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9856,0.0096,0.0014,0.0014</t>
+  </si>
+  <si>
+    <t>0.9883,0.0094,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.9976,0.0002,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9926,0.0009,0.0001,0.0031</t>
+  </si>
+  <si>
+    <t>0.9875,0.0032,0.0005,0.0036</t>
+  </si>
+  <si>
+    <t>0.9969,0.0007,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9798,0.0080,0.0026,0.0034</t>
+  </si>
+  <si>
+    <t>0.9929,0.0022,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9952,0.0006,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9936,0.0035,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.0221,0.0029,0.9770,0.0041</t>
+  </si>
+  <si>
+    <t>0.1609,0.0337,0.8628,0.0041</t>
+  </si>
+  <si>
+    <t>0.8054,0.0044,0.1596,0.0171</t>
+  </si>
+  <si>
+    <t>0.2044,0.0187,0.8045,0.0094</t>
+  </si>
+  <si>
+    <t>0.0549,0.9474,0.0052,0.0017</t>
+  </si>
+  <si>
+    <t>0.0324,0.9660,0.0035,0.0007</t>
+  </si>
+  <si>
+    <t>0.0496,0.9429,0.0023,0.0022</t>
+  </si>
+  <si>
+    <t>0.2629,0.7588,0.0334,0.0039</t>
+  </si>
+  <si>
+    <t>0.1617,0.8628,0.0191,0.0031</t>
+  </si>
+  <si>
+    <t>0.0094,0.9813,0.0025,0.0005</t>
+  </si>
+  <si>
+    <t>0.6128,0.4597,0.0199,0.0008</t>
+  </si>
+  <si>
+    <t>0.1924,0.6325,0.1084,0.2905</t>
+  </si>
+  <si>
+    <t>0.0326,0.0123,0.9605,0.0077</t>
+  </si>
+  <si>
+    <t>0.1599,0.7352,0.0695,0.0505</t>
+  </si>
+  <si>
+    <t>0.5263,0.1115,0.4154,0.0321</t>
+  </si>
+  <si>
+    <t>0.0153,0.1384,0.0050,0.9724</t>
+  </si>
+  <si>
+    <t>0.0117,0.9802,0.0062,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.9841,0.0028,0.0139</t>
+  </si>
+  <si>
+    <t>0.0212,0.9022,0.0474,0.0737</t>
+  </si>
+  <si>
+    <t>0.0012,0.9454,0.8250,0.0002</t>
+  </si>
+  <si>
+    <t>0.0056,0.9902,0.0111,0.0001</t>
+  </si>
+  <si>
+    <t>0.8541,0.1792,0.0227,0.0021</t>
+  </si>
+  <si>
+    <t>0.7067,0.3784,0.0201,0.0039</t>
+  </si>
+  <si>
+    <t>0.9264,0.0339,0.0144,0.0211</t>
+  </si>
+  <si>
+    <t>0.9804,0.0038,0.0029,0.0049</t>
+  </si>
+  <si>
+    <t>0.9862,0.0011,0.0002,0.0089</t>
+  </si>
+  <si>
+    <t>0.9810,0.0013,0.0022,0.0083</t>
+  </si>
+  <si>
+    <t>0.9788,0.0064,0.0034,0.0035</t>
+  </si>
+  <si>
+    <t>0.9105,0.0173,0.0802,0.0059</t>
+  </si>
+  <si>
+    <t>0.9768,0.0082,0.0024,0.0052</t>
+  </si>
+  <si>
+    <t>0.9925,0.0012,0.0005,0.0018</t>
+  </si>
+  <si>
+    <t>0.0019,0.8614,0.9465,0.0005</t>
+  </si>
+  <si>
+    <t>0.0025,0.2042,0.9847,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.7584,0.9062,0.0003</t>
+  </si>
+  <si>
+    <t>0.0189,0.1661,0.9270,0.0072</t>
+  </si>
+  <si>
+    <t>0.6243,0.0684,0.1459,0.2219</t>
+  </si>
+  <si>
+    <t>0.7157,0.0443,0.2006,0.0372</t>
+  </si>
+  <si>
+    <t>0.3700,0.0233,0.7139,0.0150</t>
+  </si>
+  <si>
+    <t>0.1991,0.6016,0.2533,0.0179</t>
+  </si>
+  <si>
+    <t>0.0229,0.0011,0.0002,0.9938</t>
+  </si>
+  <si>
+    <t>0.0008,0.0031,0.0007,0.9989</t>
+  </si>
+  <si>
+    <t>0.0035,0.0200,0.0014,0.9957</t>
+  </si>
+  <si>
+    <t>0.0089,0.0011,0.0018,0.9953</t>
+  </si>
+  <si>
+    <t>0.0020,0.7092,0.9496,0.0002</t>
+  </si>
+  <si>
+    <t>0.9711,0.0100,0.0027,0.0070</t>
+  </si>
+  <si>
+    <t>0.5941,0.4366,0.0283,0.0062</t>
+  </si>
+  <si>
+    <t>0.9693,0.0122,0.0031,0.0058</t>
+  </si>
+  <si>
+    <t>0.8089,0.2353,0.0166,0.0030</t>
+  </si>
+  <si>
+    <t>0.9711,0.0051,0.0102,0.0045</t>
+  </si>
+  <si>
+    <t>0.1964,0.0188,0.0808,0.8173</t>
+  </si>
+  <si>
+    <t>0.9845,0.0034,0.0037,0.0022</t>
+  </si>
+  <si>
+    <t>0.0008,0.0326,0.9765,0.0307</t>
+  </si>
+  <si>
+    <t>0.9216,0.0023,0.0070,0.0596</t>
+  </si>
+  <si>
+    <t>0.9610,0.0007,0.0033,0.0189</t>
+  </si>
+  <si>
+    <t>0.2694,0.7969,0.0096,0.0018</t>
+  </si>
+  <si>
+    <t>0.9215,0.0247,0.0024,0.0195</t>
+  </si>
+  <si>
+    <t>0.9385,0.0332,0.0100,0.0039</t>
+  </si>
+  <si>
+    <t>0.1723,0.8337,0.0242,0.0174</t>
+  </si>
+  <si>
+    <t>0.8468,0.1273,0.0246,0.0087</t>
+  </si>
+  <si>
+    <t>0.8297,0.1560,0.0265,0.0117</t>
+  </si>
+  <si>
+    <t>0.9909,0.0027,0.0004,0.0020</t>
+  </si>
+  <si>
+    <t>0.9862,0.0071,0.0011,0.0019</t>
+  </si>
+  <si>
+    <t>0.9659,0.0303,0.0028,0.0030</t>
+  </si>
+  <si>
+    <t>0.9913,0.0006,0.0019,0.0020</t>
+  </si>
+  <si>
+    <t>0.9780,0.0080,0.0065,0.0019</t>
+  </si>
+  <si>
+    <t>0.9696,0.0081,0.0019,0.0096</t>
+  </si>
+  <si>
+    <t>0.9776,0.0087,0.0030,0.0038</t>
+  </si>
+  <si>
+    <t>0.9881,0.0009,0.0003,0.0062</t>
+  </si>
+  <si>
+    <t>0.5305,0.5100,0.0089,0.0173</t>
+  </si>
+  <si>
+    <t>0.8013,0.2543,0.0198,0.0017</t>
+  </si>
+  <si>
+    <t>0.6036,0.4516,0.0228,0.0084</t>
+  </si>
+  <si>
+    <t>0.3133,0.4961,0.3331,0.0051</t>
+  </si>
+  <si>
+    <t>0.9263,0.0930,0.0031,0.0026</t>
+  </si>
+  <si>
+    <t>0.9145,0.0554,0.0124,0.0137</t>
+  </si>
+  <si>
+    <t>0.9411,0.0440,0.0037,0.0083</t>
+  </si>
+  <si>
+    <t>0.9272,0.0141,0.0278,0.0172</t>
+  </si>
+  <si>
+    <t>0.0014,0.0251,0.9876,0.0021</t>
+  </si>
+  <si>
+    <t>0.8318,0.1973,0.0048,0.0079</t>
+  </si>
+  <si>
+    <t>0.0025,0.0132,0.9935,0.0006</t>
+  </si>
+  <si>
+    <t>0.0124,0.1490,0.9600,0.0070</t>
+  </si>
+  <si>
+    <t>0.2501,0.0317,0.8231,0.0015</t>
+  </si>
+  <si>
+    <t>0.0139,0.1135,0.9543,0.0025</t>
+  </si>
+  <si>
+    <t>0.0050,0.0187,0.9844,0.0060</t>
+  </si>
+  <si>
+    <t>0.0137,0.0022,0.9842,0.0013</t>
+  </si>
+  <si>
+    <t>0.0164,0.0069,0.9820,0.0010</t>
+  </si>
+  <si>
+    <t>0.3074,0.0252,0.7882,0.0037</t>
+  </si>
+  <si>
+    <t>0.0731,0.0139,0.9246,0.0106</t>
+  </si>
+  <si>
+    <t>0.7518,0.0154,0.2688,0.0163</t>
+  </si>
+  <si>
+    <t>0.4797,0.2283,0.2068,0.0055</t>
+  </si>
+  <si>
+    <t>0.1083,0.6168,0.3098,0.0013</t>
+  </si>
+  <si>
+    <t>0.6449,0.1726,0.1797,0.0043</t>
+  </si>
+  <si>
+    <t>0.6909,0.0944,0.2423,0.0167</t>
+  </si>
+  <si>
+    <t>0.3728,0.1308,0.5932,0.0064</t>
+  </si>
+  <si>
+    <t>0.8631,0.2095,0.0065,0.0012</t>
+  </si>
+  <si>
+    <t>0.6929,0.5045,0.0021,0.0012</t>
+  </si>
+  <si>
+    <t>0.8740,0.2355,0.0017,0.0011</t>
+  </si>
+  <si>
+    <t>0.9817,0.0133,0.0007,0.0015</t>
+  </si>
+  <si>
+    <t>0.9330,0.1118,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.5429,0.2396,0.3141,0.0463</t>
+  </si>
+  <si>
+    <t>0.9090,0.0047,0.0543,0.0065</t>
+  </si>
+  <si>
+    <t>0.8232,0.0140,0.0922,0.0247</t>
+  </si>
+  <si>
+    <t>0.4454,0.0382,0.6037,0.0285</t>
+  </si>
+  <si>
+    <t>0.8765,0.0076,0.0807,0.0140</t>
+  </si>
+  <si>
+    <t>0.3068,0.0612,0.6237,0.0628</t>
+  </si>
+  <si>
+    <t>0.0386,0.0151,0.9579,0.0028</t>
+  </si>
+  <si>
+    <t>0.0468,0.0709,0.9095,0.0011</t>
+  </si>
+  <si>
+    <t>0.0345,0.1561,0.9217,0.0126</t>
+  </si>
+  <si>
+    <t>0.0017,0.9559,0.1625,0.0003</t>
+  </si>
+  <si>
+    <t>0.9904,0.0022,0.0004,0.0029</t>
+  </si>
+  <si>
+    <t>0.9920,0.0034,0.0016,0.0004</t>
+  </si>
+  <si>
+    <t>0.9750,0.0123,0.0003,0.0045</t>
+  </si>
+  <si>
+    <t>0.9727,0.0246,0.0022,0.0019</t>
+  </si>
+  <si>
+    <t>0.9574,0.0495,0.0046,0.0019</t>
+  </si>
+  <si>
+    <t>0.9792,0.0121,0.0015,0.0030</t>
+  </si>
+  <si>
+    <t>0.9748,0.0019,0.0010,0.0155</t>
+  </si>
+  <si>
+    <t>0.9844,0.0094,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.0479,0.0425,0.9310,0.0027</t>
+  </si>
+  <si>
+    <t>0.1753,0.3016,0.6597,0.0612</t>
+  </si>
+  <si>
+    <t>0.8278,0.0115,0.1043,0.0285</t>
+  </si>
+  <si>
+    <t>0.0121,0.0248,0.9639,0.0086</t>
+  </si>
+  <si>
+    <t>0.0014,0.0204,0.9868,0.0022</t>
+  </si>
+  <si>
+    <t>0.0022,0.7893,0.5972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0015,0.9982,0.0012</t>
+  </si>
+  <si>
+    <t>0.0521,0.0273,0.9207,0.0060</t>
+  </si>
+  <si>
+    <t>0.0089,0.0091,0.9884,0.0010</t>
+  </si>
+  <si>
+    <t>0.0098,0.0321,0.9477,0.0140</t>
+  </si>
+  <si>
+    <t>0.2908,0.1868,0.6077,0.0222</t>
+  </si>
+  <si>
+    <t>0.7283,0.0026,0.1066,0.0681</t>
+  </si>
+  <si>
+    <t>0.4967,0.0067,0.6395,0.0078</t>
+  </si>
+  <si>
+    <t>0.9200,0.0083,0.0535,0.0026</t>
+  </si>
+  <si>
+    <t>0.9852,0.0065,0.0006,0.0030</t>
+  </si>
+  <si>
+    <t>0.9894,0.0046,0.0003,0.0020</t>
+  </si>
+  <si>
+    <t>0.9869,0.0098,0.0019,0.0006</t>
+  </si>
+  <si>
+    <t>0.9572,0.0484,0.0024,0.0021</t>
+  </si>
+  <si>
+    <t>0.9875,0.0014,0.0001,0.0058</t>
+  </si>
+  <si>
+    <t>0.9868,0.0117,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.9938,0.0025,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9886,0.0031,0.0005,0.0030</t>
+  </si>
+  <si>
+    <t>0.0661,0.0322,0.8878,0.0190</t>
+  </si>
+  <si>
+    <t>0.0014,0.0791,0.9773,0.0019</t>
+  </si>
+  <si>
+    <t>0.0127,0.0789,0.9617,0.0014</t>
+  </si>
+  <si>
+    <t>0.1177,0.0424,0.7817,0.0003</t>
+  </si>
+  <si>
+    <t>0.0078,0.0320,0.9698,0.0075</t>
+  </si>
+  <si>
+    <t>0.0939,0.0209,0.8804,0.0278</t>
+  </si>
+  <si>
+    <t>0.0629,0.0053,0.9481,0.0015</t>
+  </si>
+  <si>
+    <t>0.0520,0.0551,0.8759,0.0499</t>
+  </si>
+  <si>
+    <t>0.8796,0.0003,0.0025,0.1327</t>
+  </si>
+  <si>
+    <t>0.0129,0.1366,0.0060,0.9805</t>
+  </si>
+  <si>
+    <t>0.0096,0.0045,0.0019,0.9944</t>
+  </si>
+  <si>
+    <t>0.0014,0.0003,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.0080,0.0054,0.0019,0.9943</t>
+  </si>
+  <si>
+    <t>0.8026,0.0460,0.0366,0.0754</t>
   </si>
 </sst>
 </file>
@@ -1953,10 +1968,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1996,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2013,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2136,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2153,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2167,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2195,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2234,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2276,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2290,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2374,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2388,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2419,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2447,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2461,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2489,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2545,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2559,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2657,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2755,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2825,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2867,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2923,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2934,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2965,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2979,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2993,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3007,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3105,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3116,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3133,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3147,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3161,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3175,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3441,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3553,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3564,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3581,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3592,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3609,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3620,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3679,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3704,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3718,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3847,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3861,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3872,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3928,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3942,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3959,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4012,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4040,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4071,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4096,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4127,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4169,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4208,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4362,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4379,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4393,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4404,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4421,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4435,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4463,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4603,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4617,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4628,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4642,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4659,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4670,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4687,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4701,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4712,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4726,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4743,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4771,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4782,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4824,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4866,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4883,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4897,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4908,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5051,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5104,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5135,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5177,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5202,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5387,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5415,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5429,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5457,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5485,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5527,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
